--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_394_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_394_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>8</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>61:19</t>
+          <t>31:31</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>52:04</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -1923,16 +1923,16 @@
         <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>7</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>55:59</t>
+          <t>36:00</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>49:29</t>
+          <t>29:41</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>52:58</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>30:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>48:27</t>
+          <t>28:28</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -3631,16 +3631,16 @@
         <v>92</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>29</v>
@@ -4096,10 +4096,10 @@
         <v>19</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>45:01</t>
+          <t>25:13</t>
         </is>
       </c>
       <c r="AN34" t="n">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>32:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>3</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>48:07</t>
+          <t>28:08</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>27.4%</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
         <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>49:25</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -5076,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>40:06</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>87.1%</t>
         </is>
       </c>
     </row>
@@ -5468,16 +5468,16 @@
         <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>3</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>54:05</t>
+          <t>24:17</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -5664,16 +5664,16 @@
         <v>8</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>4</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -6056,10 +6056,10 @@
         <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>49:08</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,22 +6172,22 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>30:24</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
           <t>4.7%</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6588,16 +6588,16 @@
         <v>68</v>
       </c>
       <c r="T47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
         <v>18</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_394_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_394_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X18" t="n">
         <v>8</v>
@@ -1923,16 +1923,16 @@
         <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
         <v>7</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3631,16 +3631,16 @@
         <v>92</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X29" t="n">
         <v>29</v>
@@ -4096,10 +4096,10 @@
         <v>19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>3</v>
@@ -4684,7 +4684,7 @@
         <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>3</v>
@@ -5664,16 +5664,16 @@
         <v>8</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>4</v>
@@ -6056,10 +6056,10 @@
         <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>68</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
         <v>18</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_394_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_394_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -851,20 +851,20 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>5</v>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,10 +1935,10 @@
         <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3643,14 +3643,14 @@
         <v>9</v>
       </c>
       <c r="X29" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="AA29" t="n">
@@ -4108,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -4337,25 +4337,25 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -4500,14 +4500,14 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
@@ -5135,11 +5135,11 @@
         <v>1</v>
       </c>
       <c r="AK39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,10 +5676,10 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6600,14 +6600,14 @@
         <v>4</v>
       </c>
       <c r="X47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -6644,14 +6644,14 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK47" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
